--- a/output/version3/test/10-5/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="C2" t="n">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="D2" t="n">
-        <v>468</v>
+        <v>430</v>
       </c>
       <c r="E2" t="n">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="F2" t="n">
-        <v>478</v>
+        <v>444</v>
       </c>
       <c r="G2" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H2" t="n">
-        <v>436</v>
+        <v>369</v>
       </c>
       <c r="I2" t="n">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="J2" t="n">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="K2" t="n">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="L2" t="n">
-        <v>452.2</v>
+        <v>438.8</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
+        <v>465</v>
+      </c>
+      <c r="C3" t="n">
+        <v>512</v>
+      </c>
+      <c r="D3" t="n">
+        <v>417</v>
+      </c>
+      <c r="E3" t="n">
+        <v>596</v>
+      </c>
+      <c r="F3" t="n">
         <v>444</v>
       </c>
-      <c r="C3" t="n">
-        <v>437</v>
-      </c>
-      <c r="D3" t="n">
-        <v>463</v>
-      </c>
-      <c r="E3" t="n">
-        <v>466</v>
-      </c>
-      <c r="F3" t="n">
-        <v>465</v>
-      </c>
       <c r="G3" t="n">
-        <v>512</v>
+        <v>464</v>
       </c>
       <c r="H3" t="n">
-        <v>496</v>
+        <v>560</v>
       </c>
       <c r="I3" t="n">
-        <v>508</v>
+        <v>460</v>
       </c>
       <c r="J3" t="n">
-        <v>491</v>
+        <v>541</v>
       </c>
       <c r="K3" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="L3" t="n">
-        <v>471.5</v>
+        <v>490.4</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>513</v>
+        <v>592</v>
       </c>
       <c r="C4" t="n">
-        <v>461</v>
+        <v>537</v>
       </c>
       <c r="D4" t="n">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E4" t="n">
-        <v>557</v>
+        <v>488</v>
       </c>
       <c r="F4" t="n">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="G4" t="n">
-        <v>489</v>
+        <v>529</v>
       </c>
       <c r="H4" t="n">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="I4" t="n">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="J4" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="L4" t="n">
-        <v>501.7</v>
+        <v>517.2</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>408</v>
+        <v>494</v>
       </c>
       <c r="C5" t="n">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="D5" t="n">
-        <v>483</v>
+        <v>421</v>
       </c>
       <c r="E5" t="n">
-        <v>492</v>
+        <v>447</v>
       </c>
       <c r="F5" t="n">
-        <v>491</v>
+        <v>441</v>
       </c>
       <c r="G5" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H5" t="n">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="I5" t="n">
-        <v>475</v>
+        <v>441</v>
       </c>
       <c r="J5" t="n">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="K5" t="n">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="L5" t="n">
-        <v>473.7</v>
+        <v>465.2</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C6" t="n">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="D6" t="n">
         <v>442</v>
       </c>
       <c r="E6" t="n">
-        <v>534</v>
+        <v>443</v>
       </c>
       <c r="F6" t="n">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="G6" t="n">
-        <v>460</v>
+        <v>428</v>
       </c>
       <c r="H6" t="n">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="I6" t="n">
-        <v>554</v>
+        <v>474</v>
       </c>
       <c r="J6" t="n">
-        <v>438</v>
+        <v>541</v>
       </c>
       <c r="K6" t="n">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="L6" t="n">
-        <v>465.7</v>
+        <v>454.6</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C7" t="n">
+        <v>432</v>
+      </c>
+      <c r="D7" t="n">
+        <v>450</v>
+      </c>
+      <c r="E7" t="n">
+        <v>425</v>
+      </c>
+      <c r="F7" t="n">
         <v>483</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
+        <v>510</v>
+      </c>
+      <c r="H7" t="n">
         <v>458</v>
       </c>
-      <c r="E7" t="n">
-        <v>478</v>
-      </c>
-      <c r="F7" t="n">
-        <v>489</v>
-      </c>
-      <c r="G7" t="n">
-        <v>471</v>
-      </c>
-      <c r="H7" t="n">
-        <v>405</v>
-      </c>
       <c r="I7" t="n">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="J7" t="n">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="K7" t="n">
-        <v>459</v>
+        <v>411</v>
       </c>
       <c r="L7" t="n">
-        <v>466.9</v>
+        <v>459.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>526</v>
+        <v>479</v>
       </c>
       <c r="C8" t="n">
         <v>478</v>
       </c>
       <c r="D8" t="n">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="E8" t="n">
-        <v>550</v>
+        <v>476</v>
       </c>
       <c r="F8" t="n">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="G8" t="n">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="H8" t="n">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="I8" t="n">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="J8" t="n">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="K8" t="n">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="L8" t="n">
-        <v>507</v>
+        <v>501.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
+        <v>457</v>
+      </c>
+      <c r="C9" t="n">
+        <v>504</v>
+      </c>
+      <c r="D9" t="n">
+        <v>479</v>
+      </c>
+      <c r="E9" t="n">
+        <v>458</v>
+      </c>
+      <c r="F9" t="n">
+        <v>442</v>
+      </c>
+      <c r="G9" t="n">
+        <v>414</v>
+      </c>
+      <c r="H9" t="n">
         <v>443</v>
       </c>
-      <c r="C9" t="n">
-        <v>458</v>
-      </c>
-      <c r="D9" t="n">
-        <v>473</v>
-      </c>
-      <c r="E9" t="n">
-        <v>526</v>
-      </c>
-      <c r="F9" t="n">
-        <v>440</v>
-      </c>
-      <c r="G9" t="n">
-        <v>420</v>
-      </c>
-      <c r="H9" t="n">
-        <v>407</v>
-      </c>
       <c r="I9" t="n">
-        <v>507</v>
+        <v>391</v>
       </c>
       <c r="J9" t="n">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="K9" t="n">
-        <v>403</v>
+        <v>486</v>
       </c>
       <c r="L9" t="n">
-        <v>452.1</v>
+        <v>453.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>471</v>
+        <v>534</v>
       </c>
       <c r="C10" t="n">
-        <v>571</v>
+        <v>488</v>
       </c>
       <c r="D10" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="E10" t="n">
-        <v>463</v>
+        <v>547</v>
       </c>
       <c r="F10" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="G10" t="n">
-        <v>445</v>
+        <v>523</v>
       </c>
       <c r="H10" t="n">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="I10" t="n">
-        <v>472</v>
+        <v>537</v>
       </c>
       <c r="J10" t="n">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="K10" t="n">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="L10" t="n">
-        <v>488.2</v>
+        <v>509.7</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>477</v>
+        <v>513</v>
       </c>
       <c r="C11" t="n">
-        <v>472</v>
+        <v>519</v>
       </c>
       <c r="D11" t="n">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="E11" t="n">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="F11" t="n">
-        <v>452</v>
+        <v>485</v>
       </c>
       <c r="G11" t="n">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="H11" t="n">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="I11" t="n">
-        <v>492</v>
+        <v>429</v>
       </c>
       <c r="J11" t="n">
-        <v>479</v>
+        <v>413</v>
       </c>
       <c r="K11" t="n">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="L11" t="n">
-        <v>458.1</v>
+        <v>453.6</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="C12" t="n">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="D12" t="n">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="E12" t="n">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F12" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="G12" t="n">
+        <v>519</v>
+      </c>
+      <c r="H12" t="n">
+        <v>514</v>
+      </c>
+      <c r="I12" t="n">
+        <v>483</v>
+      </c>
+      <c r="J12" t="n">
+        <v>520</v>
+      </c>
+      <c r="K12" t="n">
         <v>473</v>
       </c>
-      <c r="H12" t="n">
-        <v>551</v>
-      </c>
-      <c r="I12" t="n">
-        <v>537</v>
-      </c>
-      <c r="J12" t="n">
-        <v>506</v>
-      </c>
-      <c r="K12" t="n">
-        <v>545</v>
-      </c>
       <c r="L12" t="n">
-        <v>517.8</v>
+        <v>502.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="C13" t="n">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="D13" t="n">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="E13" t="n">
-        <v>540</v>
+        <v>456</v>
       </c>
       <c r="F13" t="n">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="G13" t="n">
-        <v>599</v>
+        <v>464</v>
       </c>
       <c r="H13" t="n">
-        <v>521</v>
+        <v>452</v>
       </c>
       <c r="I13" t="n">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="J13" t="n">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="K13" t="n">
-        <v>554</v>
+        <v>485</v>
       </c>
       <c r="L13" t="n">
-        <v>510.3</v>
+        <v>480.7</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>469</v>
+        <v>522</v>
       </c>
       <c r="C14" t="n">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="D14" t="n">
-        <v>528</v>
+        <v>497</v>
       </c>
       <c r="E14" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F14" t="n">
-        <v>539</v>
+        <v>436</v>
       </c>
       <c r="G14" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="H14" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="I14" t="n">
+        <v>455</v>
+      </c>
+      <c r="J14" t="n">
+        <v>487</v>
+      </c>
+      <c r="K14" t="n">
+        <v>562</v>
+      </c>
+      <c r="L14" t="n">
         <v>495</v>
-      </c>
-      <c r="J14" t="n">
-        <v>450</v>
-      </c>
-      <c r="K14" t="n">
-        <v>466</v>
-      </c>
-      <c r="L14" t="n">
-        <v>493.9</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C15" t="n">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="D15" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E15" t="n">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F15" t="n">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="G15" t="n">
-        <v>403</v>
+        <v>455</v>
       </c>
       <c r="H15" t="n">
-        <v>489</v>
+        <v>424</v>
       </c>
       <c r="I15" t="n">
-        <v>456</v>
+        <v>428</v>
       </c>
       <c r="J15" t="n">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="K15" t="n">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="L15" t="n">
-        <v>460.5</v>
+        <v>451.5</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C16" t="n">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="D16" t="n">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="E16" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F16" t="n">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="G16" t="n">
-        <v>491</v>
+        <v>407</v>
       </c>
       <c r="H16" t="n">
-        <v>416</v>
+        <v>473</v>
       </c>
       <c r="I16" t="n">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="J16" t="n">
-        <v>448</v>
+        <v>508</v>
       </c>
       <c r="K16" t="n">
-        <v>419</v>
+        <v>469</v>
       </c>
       <c r="L16" t="n">
-        <v>447</v>
+        <v>458.6</v>
       </c>
     </row>
     <row r="17">
@@ -1044,34 +1044,34 @@
         <v>471</v>
       </c>
       <c r="C17" t="n">
+        <v>472</v>
+      </c>
+      <c r="D17" t="n">
+        <v>499</v>
+      </c>
+      <c r="E17" t="n">
+        <v>471</v>
+      </c>
+      <c r="F17" t="n">
+        <v>485</v>
+      </c>
+      <c r="G17" t="n">
+        <v>409</v>
+      </c>
+      <c r="H17" t="n">
+        <v>497</v>
+      </c>
+      <c r="I17" t="n">
         <v>408</v>
       </c>
-      <c r="D17" t="n">
-        <v>517</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="J17" t="n">
+        <v>392</v>
+      </c>
+      <c r="K17" t="n">
         <v>491</v>
       </c>
-      <c r="F17" t="n">
-        <v>426</v>
-      </c>
-      <c r="G17" t="n">
-        <v>429</v>
-      </c>
-      <c r="H17" t="n">
-        <v>476</v>
-      </c>
-      <c r="I17" t="n">
-        <v>442</v>
-      </c>
-      <c r="J17" t="n">
-        <v>483</v>
-      </c>
-      <c r="K17" t="n">
-        <v>377</v>
-      </c>
       <c r="L17" t="n">
-        <v>452</v>
+        <v>459.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>516</v>
+        <v>445</v>
       </c>
       <c r="C18" t="n">
-        <v>459</v>
+        <v>543</v>
       </c>
       <c r="D18" t="n">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E18" t="n">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F18" t="n">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="G18" t="n">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="H18" t="n">
-        <v>521</v>
+        <v>450</v>
       </c>
       <c r="I18" t="n">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="J18" t="n">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="K18" t="n">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="L18" t="n">
-        <v>489.6</v>
+        <v>486.7</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>512</v>
+        <v>458</v>
       </c>
       <c r="C19" t="n">
         <v>468</v>
       </c>
       <c r="D19" t="n">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="E19" t="n">
-        <v>535</v>
+        <v>466</v>
       </c>
       <c r="F19" t="n">
+        <v>492</v>
+      </c>
+      <c r="G19" t="n">
+        <v>515</v>
+      </c>
+      <c r="H19" t="n">
+        <v>472</v>
+      </c>
+      <c r="I19" t="n">
+        <v>478</v>
+      </c>
+      <c r="J19" t="n">
+        <v>493</v>
+      </c>
+      <c r="K19" t="n">
         <v>566</v>
       </c>
-      <c r="G19" t="n">
-        <v>419</v>
-      </c>
-      <c r="H19" t="n">
-        <v>457</v>
-      </c>
-      <c r="I19" t="n">
-        <v>491</v>
-      </c>
-      <c r="J19" t="n">
-        <v>457</v>
-      </c>
-      <c r="K19" t="n">
-        <v>558</v>
-      </c>
       <c r="L19" t="n">
-        <v>495.4</v>
+        <v>487.2</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>537</v>
+        <v>492</v>
       </c>
       <c r="C20" t="n">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="D20" t="n">
-        <v>453</v>
+        <v>552</v>
       </c>
       <c r="E20" t="n">
-        <v>526</v>
+        <v>464</v>
       </c>
       <c r="F20" t="n">
-        <v>483</v>
+        <v>428</v>
       </c>
       <c r="G20" t="n">
-        <v>442</v>
+        <v>420</v>
       </c>
       <c r="H20" t="n">
-        <v>518</v>
+        <v>438</v>
       </c>
       <c r="I20" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="J20" t="n">
-        <v>462</v>
+        <v>612</v>
       </c>
       <c r="K20" t="n">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="L20" t="n">
-        <v>490.3</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C21" t="n">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D21" t="n">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E21" t="n">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="F21" t="n">
-        <v>452</v>
+        <v>417</v>
       </c>
       <c r="G21" t="n">
-        <v>468</v>
+        <v>424</v>
       </c>
       <c r="H21" t="n">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="I21" t="n">
-        <v>466</v>
+        <v>429</v>
       </c>
       <c r="J21" t="n">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="K21" t="n">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="L21" t="n">
-        <v>473.3</v>
+        <v>456.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="C22" t="n">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="D22" t="n">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="E22" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F22" t="n">
-        <v>519</v>
+        <v>452</v>
       </c>
       <c r="G22" t="n">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="H22" t="n">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="I22" t="n">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="J22" t="n">
-        <v>513</v>
+        <v>485</v>
       </c>
       <c r="K22" t="n">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="L22" t="n">
-        <v>505.6</v>
+        <v>488.5</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="C23" t="n">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D23" t="n">
-        <v>461</v>
+        <v>438</v>
       </c>
       <c r="E23" t="n">
+        <v>452</v>
+      </c>
+      <c r="F23" t="n">
         <v>441</v>
       </c>
-      <c r="F23" t="n">
-        <v>452</v>
-      </c>
       <c r="G23" t="n">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="H23" t="n">
         <v>451</v>
       </c>
       <c r="I23" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J23" t="n">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="K23" t="n">
-        <v>395</v>
+        <v>461</v>
       </c>
       <c r="L23" t="n">
-        <v>443.3</v>
+        <v>441.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>464</v>
+        <v>403</v>
       </c>
       <c r="C24" t="n">
-        <v>387</v>
+        <v>436</v>
       </c>
       <c r="D24" t="n">
-        <v>480</v>
+        <v>437</v>
       </c>
       <c r="E24" t="n">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="F24" t="n">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="G24" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="H24" t="n">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="I24" t="n">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="J24" t="n">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="K24" t="n">
-        <v>444</v>
+        <v>509</v>
       </c>
       <c r="L24" t="n">
-        <v>435.5</v>
+        <v>445.7</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="C25" t="n">
-        <v>455</v>
+        <v>373</v>
       </c>
       <c r="D25" t="n">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E25" t="n">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="F25" t="n">
-        <v>388</v>
+        <v>350</v>
       </c>
       <c r="G25" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H25" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I25" t="n">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="J25" t="n">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="K25" t="n">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="L25" t="n">
-        <v>406.7</v>
+        <v>397.4</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>471</v>
+        <v>535</v>
       </c>
       <c r="C26" t="n">
-        <v>593</v>
+        <v>537</v>
       </c>
       <c r="D26" t="n">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="E26" t="n">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="F26" t="n">
-        <v>571</v>
+        <v>538</v>
       </c>
       <c r="G26" t="n">
-        <v>570</v>
+        <v>529</v>
       </c>
       <c r="H26" t="n">
-        <v>556</v>
+        <v>590</v>
       </c>
       <c r="I26" t="n">
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="J26" t="n">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="K26" t="n">
-        <v>573</v>
+        <v>519</v>
       </c>
       <c r="L26" t="n">
-        <v>532.2</v>
+        <v>533</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C27" t="n">
-        <v>379</v>
+        <v>445</v>
       </c>
       <c r="D27" t="n">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="E27" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F27" t="n">
-        <v>399</v>
+        <v>479</v>
       </c>
       <c r="G27" t="n">
-        <v>484</v>
+        <v>436</v>
       </c>
       <c r="H27" t="n">
-        <v>458</v>
+        <v>418</v>
       </c>
       <c r="I27" t="n">
-        <v>430</v>
+        <v>385</v>
       </c>
       <c r="J27" t="n">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="K27" t="n">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="L27" t="n">
-        <v>434.6</v>
+        <v>439</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>460</v>
+        <v>424</v>
       </c>
       <c r="C28" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D28" t="n">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="E28" t="n">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="F28" t="n">
-        <v>427</v>
+        <v>479</v>
       </c>
       <c r="G28" t="n">
-        <v>498</v>
+        <v>464</v>
       </c>
       <c r="H28" t="n">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="I28" t="n">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="J28" t="n">
+        <v>443</v>
+      </c>
+      <c r="K28" t="n">
         <v>457</v>
       </c>
-      <c r="K28" t="n">
-        <v>471</v>
-      </c>
       <c r="L28" t="n">
-        <v>461.1</v>
+        <v>465.7</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>458</v>
+        <v>417</v>
       </c>
       <c r="C29" t="n">
-        <v>472</v>
+        <v>410</v>
       </c>
       <c r="D29" t="n">
-        <v>503</v>
+        <v>411</v>
       </c>
       <c r="E29" t="n">
+        <v>463</v>
+      </c>
+      <c r="F29" t="n">
+        <v>460</v>
+      </c>
+      <c r="G29" t="n">
+        <v>491</v>
+      </c>
+      <c r="H29" t="n">
         <v>445</v>
       </c>
-      <c r="F29" t="n">
-        <v>400</v>
-      </c>
-      <c r="G29" t="n">
-        <v>425</v>
-      </c>
-      <c r="H29" t="n">
-        <v>446</v>
-      </c>
       <c r="I29" t="n">
-        <v>455</v>
+        <v>499</v>
       </c>
       <c r="J29" t="n">
-        <v>460</v>
+        <v>398</v>
       </c>
       <c r="K29" t="n">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="L29" t="n">
-        <v>447.5</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>407</v>
+        <v>459</v>
       </c>
       <c r="C30" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="D30" t="n">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="E30" t="n">
-        <v>382</v>
+        <v>497</v>
       </c>
       <c r="F30" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G30" t="n">
-        <v>471</v>
+        <v>365</v>
       </c>
       <c r="H30" t="n">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="I30" t="n">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="J30" t="n">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="K30" t="n">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="L30" t="n">
-        <v>432.6</v>
+        <v>442.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="C31" t="n">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="D31" t="n">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="E31" t="n">
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="F31" t="n">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="G31" t="n">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="H31" t="n">
-        <v>464</v>
+        <v>504</v>
       </c>
       <c r="I31" t="n">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="J31" t="n">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="K31" t="n">
-        <v>394</v>
+        <v>482</v>
       </c>
       <c r="L31" t="n">
-        <v>461.5</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C32" t="n">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="D32" t="n">
-        <v>495</v>
+        <v>408</v>
       </c>
       <c r="E32" t="n">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="F32" t="n">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="G32" t="n">
-        <v>448</v>
+        <v>406</v>
       </c>
       <c r="H32" t="n">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="I32" t="n">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="J32" t="n">
-        <v>392</v>
+        <v>483</v>
       </c>
       <c r="K32" t="n">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L32" t="n">
-        <v>418.7</v>
+        <v>417.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>372</v>
+        <v>415</v>
       </c>
       <c r="C33" t="n">
-        <v>370</v>
+        <v>445</v>
       </c>
       <c r="D33" t="n">
-        <v>410</v>
+        <v>360</v>
       </c>
       <c r="E33" t="n">
-        <v>354</v>
+        <v>435</v>
       </c>
       <c r="F33" t="n">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="G33" t="n">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="H33" t="n">
-        <v>362</v>
+        <v>435</v>
       </c>
       <c r="I33" t="n">
-        <v>425</v>
+        <v>390</v>
       </c>
       <c r="J33" t="n">
-        <v>391</v>
+        <v>467</v>
       </c>
       <c r="K33" t="n">
-        <v>386</v>
+        <v>455</v>
       </c>
       <c r="L33" t="n">
-        <v>388.6</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="34">
@@ -1690,34 +1690,34 @@
         <v>420</v>
       </c>
       <c r="C34" t="n">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D34" t="n">
-        <v>414</v>
+        <v>488</v>
       </c>
       <c r="E34" t="n">
-        <v>413</v>
+        <v>474</v>
       </c>
       <c r="F34" t="n">
-        <v>460</v>
+        <v>421</v>
       </c>
       <c r="G34" t="n">
-        <v>432</v>
+        <v>379</v>
       </c>
       <c r="H34" t="n">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="I34" t="n">
-        <v>494</v>
+        <v>445</v>
       </c>
       <c r="J34" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K34" t="n">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="L34" t="n">
-        <v>440.7</v>
+        <v>438.7</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="C35" t="n">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="D35" t="n">
+        <v>461</v>
+      </c>
+      <c r="E35" t="n">
+        <v>473</v>
+      </c>
+      <c r="F35" t="n">
+        <v>490</v>
+      </c>
+      <c r="G35" t="n">
+        <v>416</v>
+      </c>
+      <c r="H35" t="n">
+        <v>423</v>
+      </c>
+      <c r="I35" t="n">
         <v>431</v>
       </c>
-      <c r="E35" t="n">
-        <v>409</v>
-      </c>
-      <c r="F35" t="n">
-        <v>483</v>
-      </c>
-      <c r="G35" t="n">
-        <v>483</v>
-      </c>
-      <c r="H35" t="n">
-        <v>496</v>
-      </c>
-      <c r="I35" t="n">
-        <v>498</v>
-      </c>
       <c r="J35" t="n">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="K35" t="n">
-        <v>396</v>
+        <v>515</v>
       </c>
       <c r="L35" t="n">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C36" t="n">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="D36" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E36" t="n">
-        <v>355</v>
+        <v>442</v>
       </c>
       <c r="F36" t="n">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="G36" t="n">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="H36" t="n">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="I36" t="n">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="J36" t="n">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="K36" t="n">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="L36" t="n">
-        <v>363.5</v>
+        <v>371.6</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="C37" t="n">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D37" t="n">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="E37" t="n">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="F37" t="n">
-        <v>465</v>
+        <v>409</v>
       </c>
       <c r="G37" t="n">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="H37" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="I37" t="n">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="J37" t="n">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="K37" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L37" t="n">
-        <v>447.4</v>
+        <v>442.8</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="C38" t="n">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="D38" t="n">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="E38" t="n">
-        <v>538</v>
+        <v>632</v>
       </c>
       <c r="F38" t="n">
-        <v>523</v>
+        <v>595</v>
       </c>
       <c r="G38" t="n">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="H38" t="n">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="I38" t="n">
-        <v>488</v>
+        <v>604</v>
       </c>
       <c r="J38" t="n">
-        <v>606</v>
+        <v>472</v>
       </c>
       <c r="K38" t="n">
-        <v>504</v>
+        <v>547</v>
       </c>
       <c r="L38" t="n">
-        <v>532.7</v>
+        <v>541.4</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>436</v>
+        <v>387</v>
       </c>
       <c r="C39" t="n">
-        <v>423</v>
+        <v>375</v>
       </c>
       <c r="D39" t="n">
+        <v>410</v>
+      </c>
+      <c r="E39" t="n">
+        <v>419</v>
+      </c>
+      <c r="F39" t="n">
+        <v>421</v>
+      </c>
+      <c r="G39" t="n">
+        <v>457</v>
+      </c>
+      <c r="H39" t="n">
+        <v>364</v>
+      </c>
+      <c r="I39" t="n">
+        <v>406</v>
+      </c>
+      <c r="J39" t="n">
         <v>411</v>
       </c>
-      <c r="E39" t="n">
-        <v>348</v>
-      </c>
-      <c r="F39" t="n">
-        <v>371</v>
-      </c>
-      <c r="G39" t="n">
-        <v>393</v>
-      </c>
-      <c r="H39" t="n">
-        <v>461</v>
-      </c>
-      <c r="I39" t="n">
-        <v>459</v>
-      </c>
-      <c r="J39" t="n">
-        <v>351</v>
-      </c>
       <c r="K39" t="n">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L39" t="n">
-        <v>408.5</v>
+        <v>407.9</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C40" t="n">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="D40" t="n">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="E40" t="n">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F40" t="n">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="G40" t="n">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="H40" t="n">
-        <v>465</v>
+        <v>432</v>
       </c>
       <c r="I40" t="n">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="J40" t="n">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="K40" t="n">
-        <v>515</v>
+        <v>464</v>
       </c>
       <c r="L40" t="n">
-        <v>474.3</v>
+        <v>471.4</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>493</v>
+        <v>434</v>
       </c>
       <c r="C41" t="n">
-        <v>462</v>
+        <v>564</v>
       </c>
       <c r="D41" t="n">
-        <v>504</v>
+        <v>406</v>
       </c>
       <c r="E41" t="n">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="F41" t="n">
-        <v>533</v>
+        <v>494</v>
       </c>
       <c r="G41" t="n">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="H41" t="n">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="I41" t="n">
-        <v>419</v>
+        <v>496</v>
       </c>
       <c r="J41" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="K41" t="n">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="L41" t="n">
-        <v>487</v>
+        <v>481.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
+        <v>456</v>
+      </c>
+      <c r="C42" t="n">
+        <v>505</v>
+      </c>
+      <c r="D42" t="n">
+        <v>431</v>
+      </c>
+      <c r="E42" t="n">
+        <v>424</v>
+      </c>
+      <c r="F42" t="n">
         <v>453</v>
       </c>
-      <c r="C42" t="n">
-        <v>456</v>
-      </c>
-      <c r="D42" t="n">
-        <v>440</v>
-      </c>
-      <c r="E42" t="n">
-        <v>443</v>
-      </c>
-      <c r="F42" t="n">
-        <v>456</v>
-      </c>
       <c r="G42" t="n">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="H42" t="n">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="I42" t="n">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J42" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="K42" t="n">
-        <v>509</v>
+        <v>425</v>
       </c>
       <c r="L42" t="n">
-        <v>447.8</v>
+        <v>447.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C43" t="n">
-        <v>488</v>
+        <v>446</v>
       </c>
       <c r="D43" t="n">
         <v>436</v>
       </c>
       <c r="E43" t="n">
-        <v>421</v>
+        <v>496</v>
       </c>
       <c r="F43" t="n">
-        <v>424</v>
+        <v>466</v>
       </c>
       <c r="G43" t="n">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="H43" t="n">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="I43" t="n">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="J43" t="n">
-        <v>428</v>
+        <v>496</v>
       </c>
       <c r="K43" t="n">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="L43" t="n">
-        <v>452.8</v>
+        <v>464.7</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="C44" t="n">
+        <v>541</v>
+      </c>
+      <c r="D44" t="n">
+        <v>440</v>
+      </c>
+      <c r="E44" t="n">
+        <v>471</v>
+      </c>
+      <c r="F44" t="n">
         <v>450</v>
       </c>
-      <c r="D44" t="n">
-        <v>462</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
+        <v>475</v>
+      </c>
+      <c r="H44" t="n">
+        <v>433</v>
+      </c>
+      <c r="I44" t="n">
+        <v>474</v>
+      </c>
+      <c r="J44" t="n">
         <v>458</v>
-      </c>
-      <c r="F44" t="n">
-        <v>449</v>
-      </c>
-      <c r="G44" t="n">
-        <v>423</v>
-      </c>
-      <c r="H44" t="n">
-        <v>424</v>
-      </c>
-      <c r="I44" t="n">
-        <v>453</v>
-      </c>
-      <c r="J44" t="n">
-        <v>420</v>
       </c>
       <c r="K44" t="n">
         <v>475</v>
       </c>
       <c r="L44" t="n">
-        <v>444.2</v>
+        <v>462.1</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C45" t="n">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="D45" t="n">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="E45" t="n">
-        <v>496</v>
+        <v>418</v>
       </c>
       <c r="F45" t="n">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="G45" t="n">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="H45" t="n">
-        <v>466</v>
+        <v>579</v>
       </c>
       <c r="I45" t="n">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="J45" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="K45" t="n">
-        <v>446</v>
+        <v>518</v>
       </c>
       <c r="L45" t="n">
-        <v>457.5</v>
+        <v>474.1</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>445</v>
+        <v>374</v>
       </c>
       <c r="C46" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D46" t="n">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="E46" t="n">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="F46" t="n">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="G46" t="n">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="H46" t="n">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="I46" t="n">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="J46" t="n">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="K46" t="n">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="L46" t="n">
-        <v>406.6</v>
+        <v>392.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>506</v>
+        <v>592</v>
       </c>
       <c r="C47" t="n">
-        <v>565</v>
+        <v>464</v>
       </c>
       <c r="D47" t="n">
-        <v>553</v>
+        <v>496</v>
       </c>
       <c r="E47" t="n">
-        <v>522</v>
+        <v>475</v>
       </c>
       <c r="F47" t="n">
-        <v>513</v>
+        <v>471</v>
       </c>
       <c r="G47" t="n">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="H47" t="n">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="I47" t="n">
-        <v>586</v>
+        <v>490</v>
       </c>
       <c r="J47" t="n">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="K47" t="n">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="L47" t="n">
-        <v>519.3</v>
+        <v>493.2</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="C48" t="n">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="D48" t="n">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="E48" t="n">
-        <v>496</v>
+        <v>452</v>
       </c>
       <c r="F48" t="n">
-        <v>518</v>
+        <v>475</v>
       </c>
       <c r="G48" t="n">
-        <v>469</v>
+        <v>528</v>
       </c>
       <c r="H48" t="n">
-        <v>455</v>
+        <v>515</v>
       </c>
       <c r="I48" t="n">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="J48" t="n">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="K48" t="n">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="L48" t="n">
-        <v>489.7</v>
+        <v>490.5</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>405</v>
+        <v>488</v>
       </c>
       <c r="C49" t="n">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="D49" t="n">
+        <v>456</v>
+      </c>
+      <c r="E49" t="n">
+        <v>459</v>
+      </c>
+      <c r="F49" t="n">
         <v>492</v>
       </c>
-      <c r="E49" t="n">
-        <v>482</v>
-      </c>
-      <c r="F49" t="n">
-        <v>508</v>
-      </c>
       <c r="G49" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H49" t="n">
-        <v>393</v>
+        <v>472</v>
       </c>
       <c r="I49" t="n">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="J49" t="n">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="K49" t="n">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="L49" t="n">
-        <v>445.2</v>
+        <v>453.7</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C50" t="n">
-        <v>457</v>
+        <v>404</v>
       </c>
       <c r="D50" t="n">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E50" t="n">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="F50" t="n">
-        <v>459</v>
+        <v>376</v>
       </c>
       <c r="G50" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H50" t="n">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="I50" t="n">
-        <v>421</v>
+        <v>493</v>
       </c>
       <c r="J50" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="K50" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L50" t="n">
-        <v>427.3</v>
+        <v>414.1</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>461</v>
+        <v>381</v>
       </c>
       <c r="C51" t="n">
-        <v>463</v>
+        <v>391</v>
       </c>
       <c r="D51" t="n">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="E51" t="n">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="F51" t="n">
-        <v>391</v>
+        <v>468</v>
       </c>
       <c r="G51" t="n">
-        <v>391</v>
+        <v>462</v>
       </c>
       <c r="H51" t="n">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="I51" t="n">
-        <v>476</v>
+        <v>368</v>
       </c>
       <c r="J51" t="n">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="K51" t="n">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="L51" t="n">
-        <v>417.5</v>
+        <v>412.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>459.82</v>
+        <v>460.1</v>
       </c>
       <c r="C52" t="n">
-        <v>460.12</v>
+        <v>463.46</v>
       </c>
       <c r="D52" t="n">
-        <v>468.42</v>
+        <v>456.16</v>
       </c>
       <c r="E52" t="n">
-        <v>464.96</v>
+        <v>465.8</v>
       </c>
       <c r="F52" t="n">
-        <v>465.02</v>
+        <v>458.32</v>
       </c>
       <c r="G52" t="n">
-        <v>456.18</v>
+        <v>452.66</v>
       </c>
       <c r="H52" t="n">
-        <v>456.18</v>
+        <v>457.72</v>
       </c>
       <c r="I52" t="n">
-        <v>470.84</v>
+        <v>458.66</v>
       </c>
       <c r="J52" t="n">
-        <v>451.2</v>
+        <v>463.2</v>
       </c>
       <c r="K52" t="n">
-        <v>456.48</v>
+        <v>470.5</v>
       </c>
       <c r="L52" t="n">
-        <v>460.922</v>
+        <v>460.658</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.535554170608521</v>
+        <v>2.354325294494629</v>
       </c>
       <c r="C2" t="n">
-        <v>2.166813135147095</v>
+        <v>2.338201999664307</v>
       </c>
       <c r="D2" t="n">
-        <v>2.273499727249146</v>
+        <v>2.369868040084839</v>
       </c>
       <c r="E2" t="n">
-        <v>2.143287420272827</v>
+        <v>2.692416906356812</v>
       </c>
       <c r="F2" t="n">
-        <v>2.344024896621704</v>
+        <v>2.843831777572632</v>
       </c>
       <c r="G2" t="n">
-        <v>2.479438066482544</v>
+        <v>2.520313024520874</v>
       </c>
       <c r="H2" t="n">
-        <v>2.670813798904419</v>
+        <v>2.324810743331909</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26318883895874</v>
+        <v>2.149650573730469</v>
       </c>
       <c r="J2" t="n">
-        <v>2.275178670883179</v>
+        <v>2.298744201660156</v>
       </c>
       <c r="K2" t="n">
-        <v>2.221169233322144</v>
+        <v>2.379988670349121</v>
       </c>
       <c r="L2" t="n">
-        <v>2.337296795845032</v>
+        <v>2.427215123176575</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.340759515762329</v>
+        <v>2.485576152801514</v>
       </c>
       <c r="C3" t="n">
-        <v>2.348502397537231</v>
+        <v>2.239413738250732</v>
       </c>
       <c r="D3" t="n">
-        <v>3.920060396194458</v>
+        <v>2.295718908309937</v>
       </c>
       <c r="E3" t="n">
-        <v>2.698898792266846</v>
+        <v>2.825170040130615</v>
       </c>
       <c r="F3" t="n">
-        <v>2.211879014968872</v>
+        <v>2.160307884216309</v>
       </c>
       <c r="G3" t="n">
-        <v>2.31183123588562</v>
+        <v>2.378748655319214</v>
       </c>
       <c r="H3" t="n">
-        <v>2.159847974777222</v>
+        <v>2.60277247428894</v>
       </c>
       <c r="I3" t="n">
-        <v>2.365382194519043</v>
+        <v>2.35053014755249</v>
       </c>
       <c r="J3" t="n">
-        <v>2.265151262283325</v>
+        <v>2.601638317108154</v>
       </c>
       <c r="K3" t="n">
-        <v>2.187834501266479</v>
+        <v>2.318158626556396</v>
       </c>
       <c r="L3" t="n">
-        <v>2.481014728546143</v>
+        <v>2.42580349445343</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.330092191696167</v>
+        <v>2.845265626907349</v>
       </c>
       <c r="C4" t="n">
-        <v>2.467078924179077</v>
+        <v>2.352936267852783</v>
       </c>
       <c r="D4" t="n">
-        <v>2.320785522460938</v>
+        <v>3.245968341827393</v>
       </c>
       <c r="E4" t="n">
-        <v>2.470471382141113</v>
+        <v>2.485957622528076</v>
       </c>
       <c r="F4" t="n">
-        <v>2.302194356918335</v>
+        <v>2.613042116165161</v>
       </c>
       <c r="G4" t="n">
-        <v>2.287498950958252</v>
+        <v>2.849353313446045</v>
       </c>
       <c r="H4" t="n">
-        <v>2.364861249923706</v>
+        <v>2.615352153778076</v>
       </c>
       <c r="I4" t="n">
-        <v>2.384615898132324</v>
+        <v>3.603779315948486</v>
       </c>
       <c r="J4" t="n">
-        <v>2.355113983154297</v>
+        <v>3.326751947402954</v>
       </c>
       <c r="K4" t="n">
-        <v>2.43237042427063</v>
+        <v>3.032402753829956</v>
       </c>
       <c r="L4" t="n">
-        <v>2.371508288383484</v>
+        <v>2.897080945968628</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1.993009805679321</v>
+        <v>2.518052339553833</v>
       </c>
       <c r="C5" t="n">
-        <v>2.13019847869873</v>
+        <v>2.352627515792847</v>
       </c>
       <c r="D5" t="n">
-        <v>2.018278837203979</v>
+        <v>3.172796964645386</v>
       </c>
       <c r="E5" t="n">
-        <v>2.075641632080078</v>
+        <v>2.622769832611084</v>
       </c>
       <c r="F5" t="n">
-        <v>2.057290315628052</v>
+        <v>2.49895453453064</v>
       </c>
       <c r="G5" t="n">
-        <v>2.221758127212524</v>
+        <v>2.504358530044556</v>
       </c>
       <c r="H5" t="n">
-        <v>2.104610204696655</v>
+        <v>2.543049097061157</v>
       </c>
       <c r="I5" t="n">
-        <v>2.149398565292358</v>
+        <v>2.658170223236084</v>
       </c>
       <c r="J5" t="n">
-        <v>2.22785496711731</v>
+        <v>3.53727912902832</v>
       </c>
       <c r="K5" t="n">
-        <v>2.208046674728394</v>
+        <v>2.555529832839966</v>
       </c>
       <c r="L5" t="n">
-        <v>2.11860876083374</v>
+        <v>2.696358799934387</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1.88996958732605</v>
+        <v>2.249273300170898</v>
       </c>
       <c r="C6" t="n">
-        <v>2.217406749725342</v>
+        <v>2.891498327255249</v>
       </c>
       <c r="D6" t="n">
-        <v>1.808170318603516</v>
+        <v>2.693423986434937</v>
       </c>
       <c r="E6" t="n">
-        <v>2.086536169052124</v>
+        <v>2.110976457595825</v>
       </c>
       <c r="F6" t="n">
-        <v>1.912963628768921</v>
+        <v>2.223416566848755</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08054518699646</v>
+        <v>2.32088041305542</v>
       </c>
       <c r="H6" t="n">
-        <v>1.856542825698853</v>
+        <v>2.1162269115448</v>
       </c>
       <c r="I6" t="n">
-        <v>2.17040753364563</v>
+        <v>2.230527400970459</v>
       </c>
       <c r="J6" t="n">
-        <v>2.056347131729126</v>
+        <v>2.395463943481445</v>
       </c>
       <c r="K6" t="n">
-        <v>1.944243431091309</v>
+        <v>1.984472751617432</v>
       </c>
       <c r="L6" t="n">
-        <v>2.002313256263733</v>
+        <v>2.321616005897522</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.25895094871521</v>
+        <v>3.324947834014893</v>
       </c>
       <c r="C7" t="n">
-        <v>2.303953409194946</v>
+        <v>2.269979000091553</v>
       </c>
       <c r="D7" t="n">
-        <v>2.191555261611938</v>
+        <v>2.60905909538269</v>
       </c>
       <c r="E7" t="n">
-        <v>2.304749011993408</v>
+        <v>2.627456426620483</v>
       </c>
       <c r="F7" t="n">
-        <v>2.212907314300537</v>
+        <v>2.518444538116455</v>
       </c>
       <c r="G7" t="n">
-        <v>2.281540632247925</v>
+        <v>2.789353609085083</v>
       </c>
       <c r="H7" t="n">
-        <v>2.303062915802002</v>
+        <v>3.5001540184021</v>
       </c>
       <c r="I7" t="n">
-        <v>2.340923547744751</v>
+        <v>2.724440574645996</v>
       </c>
       <c r="J7" t="n">
-        <v>2.218729257583618</v>
+        <v>2.663761138916016</v>
       </c>
       <c r="K7" t="n">
-        <v>2.23189640045166</v>
+        <v>2.689139604568481</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2648268699646</v>
+        <v>2.771673583984375</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.376070261001587</v>
+        <v>2.849736452102661</v>
       </c>
       <c r="C8" t="n">
-        <v>2.247934103012085</v>
+        <v>4.026977777481079</v>
       </c>
       <c r="D8" t="n">
-        <v>2.406513929367065</v>
+        <v>2.49530029296875</v>
       </c>
       <c r="E8" t="n">
-        <v>2.411556243896484</v>
+        <v>2.717419862747192</v>
       </c>
       <c r="F8" t="n">
-        <v>2.284141778945923</v>
+        <v>2.979106426239014</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22156286239624</v>
+        <v>2.724997758865356</v>
       </c>
       <c r="H8" t="n">
-        <v>2.143434524536133</v>
+        <v>4.201448202133179</v>
       </c>
       <c r="I8" t="n">
-        <v>2.253828287124634</v>
+        <v>3.049929141998291</v>
       </c>
       <c r="J8" t="n">
-        <v>2.323705911636353</v>
+        <v>2.729053258895874</v>
       </c>
       <c r="K8" t="n">
-        <v>2.443945169448853</v>
+        <v>2.494302749633789</v>
       </c>
       <c r="L8" t="n">
-        <v>2.311269307136536</v>
+        <v>3.026827192306519</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.15337061882019</v>
+        <v>2.238178014755249</v>
       </c>
       <c r="C9" t="n">
-        <v>2.068220615386963</v>
+        <v>3.38092303276062</v>
       </c>
       <c r="D9" t="n">
-        <v>2.179970502853394</v>
+        <v>2.251415491104126</v>
       </c>
       <c r="E9" t="n">
-        <v>2.136698484420776</v>
+        <v>2.345522403717041</v>
       </c>
       <c r="F9" t="n">
-        <v>2.300836324691772</v>
+        <v>2.704419136047363</v>
       </c>
       <c r="G9" t="n">
-        <v>2.359105825424194</v>
+        <v>2.257564783096313</v>
       </c>
       <c r="H9" t="n">
-        <v>2.090849637985229</v>
+        <v>2.208392858505249</v>
       </c>
       <c r="I9" t="n">
-        <v>2.115255832672119</v>
+        <v>3.730713844299316</v>
       </c>
       <c r="J9" t="n">
-        <v>2.371004581451416</v>
+        <v>2.446542978286743</v>
       </c>
       <c r="K9" t="n">
-        <v>2.182676076889038</v>
+        <v>2.584214687347412</v>
       </c>
       <c r="L9" t="n">
-        <v>2.195798850059509</v>
+        <v>2.614788722991944</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.207032680511475</v>
+        <v>2.487428665161133</v>
       </c>
       <c r="C10" t="n">
-        <v>2.481825590133667</v>
+        <v>3.744931221008301</v>
       </c>
       <c r="D10" t="n">
-        <v>2.18179988861084</v>
+        <v>3.335599422454834</v>
       </c>
       <c r="E10" t="n">
-        <v>2.169387340545654</v>
+        <v>2.820828437805176</v>
       </c>
       <c r="F10" t="n">
-        <v>2.245637655258179</v>
+        <v>2.293654441833496</v>
       </c>
       <c r="G10" t="n">
-        <v>2.199577569961548</v>
+        <v>2.342537641525269</v>
       </c>
       <c r="H10" t="n">
-        <v>2.254714727401733</v>
+        <v>2.565530300140381</v>
       </c>
       <c r="I10" t="n">
-        <v>2.353254079818726</v>
+        <v>2.272220134735107</v>
       </c>
       <c r="J10" t="n">
-        <v>2.204175710678101</v>
+        <v>2.141546249389648</v>
       </c>
       <c r="K10" t="n">
-        <v>2.299014806747437</v>
+        <v>2.281688690185547</v>
       </c>
       <c r="L10" t="n">
-        <v>2.259642004966736</v>
+        <v>2.628596520423889</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1.962002277374268</v>
+        <v>2.044807195663452</v>
       </c>
       <c r="C11" t="n">
-        <v>1.960128545761108</v>
+        <v>2.209465265274048</v>
       </c>
       <c r="D11" t="n">
-        <v>2.032224893569946</v>
+        <v>1.912622690200806</v>
       </c>
       <c r="E11" t="n">
-        <v>1.970327377319336</v>
+        <v>2.01387619972229</v>
       </c>
       <c r="F11" t="n">
-        <v>1.925471544265747</v>
+        <v>1.902643203735352</v>
       </c>
       <c r="G11" t="n">
-        <v>1.934925556182861</v>
+        <v>1.914637804031372</v>
       </c>
       <c r="H11" t="n">
-        <v>1.835102319717407</v>
+        <v>1.808391094207764</v>
       </c>
       <c r="I11" t="n">
-        <v>1.994503259658813</v>
+        <v>2.067245244979858</v>
       </c>
       <c r="J11" t="n">
-        <v>2.034828662872314</v>
+        <v>1.934569835662842</v>
       </c>
       <c r="K11" t="n">
-        <v>2.185654401779175</v>
+        <v>2.045302867889404</v>
       </c>
       <c r="L11" t="n">
-        <v>1.983516883850098</v>
+        <v>1.985356140136719</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.080410242080688</v>
+        <v>2.191437959671021</v>
       </c>
       <c r="C12" t="n">
-        <v>2.184188365936279</v>
+        <v>2.293659687042236</v>
       </c>
       <c r="D12" t="n">
-        <v>2.163032293319702</v>
+        <v>2.149024724960327</v>
       </c>
       <c r="E12" t="n">
-        <v>2.336912631988525</v>
+        <v>2.097150564193726</v>
       </c>
       <c r="F12" t="n">
-        <v>2.119667291641235</v>
+        <v>2.317616701126099</v>
       </c>
       <c r="G12" t="n">
-        <v>2.071425914764404</v>
+        <v>2.047291994094849</v>
       </c>
       <c r="H12" t="n">
-        <v>2.218341827392578</v>
+        <v>2.358494997024536</v>
       </c>
       <c r="I12" t="n">
-        <v>2.199134826660156</v>
+        <v>2.071224451065063</v>
       </c>
       <c r="J12" t="n">
-        <v>2.139797210693359</v>
+        <v>2.094164371490479</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1232008934021</v>
+        <v>2.221359491348267</v>
       </c>
       <c r="L12" t="n">
-        <v>2.163611149787903</v>
+        <v>2.18414249420166</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.077253341674805</v>
+        <v>2.131072282791138</v>
       </c>
       <c r="C13" t="n">
-        <v>2.206161975860596</v>
+        <v>2.414852857589722</v>
       </c>
       <c r="D13" t="n">
-        <v>2.346293449401855</v>
+        <v>2.148531913757324</v>
       </c>
       <c r="E13" t="n">
-        <v>2.212075233459473</v>
+        <v>2.34552264213562</v>
       </c>
       <c r="F13" t="n">
-        <v>2.108793020248413</v>
+        <v>2.288688182830811</v>
       </c>
       <c r="G13" t="n">
-        <v>2.258931159973145</v>
+        <v>2.180448055267334</v>
       </c>
       <c r="H13" t="n">
-        <v>2.347002744674683</v>
+        <v>2.232309341430664</v>
       </c>
       <c r="I13" t="n">
-        <v>2.244078159332275</v>
+        <v>2.278691291809082</v>
       </c>
       <c r="J13" t="n">
-        <v>2.225271463394165</v>
+        <v>2.249286651611328</v>
       </c>
       <c r="K13" t="n">
-        <v>2.112236976623535</v>
+        <v>2.288695573806763</v>
       </c>
       <c r="L13" t="n">
-        <v>2.213809752464294</v>
+        <v>2.255809879302979</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.296818494796753</v>
+        <v>2.374953269958496</v>
       </c>
       <c r="C14" t="n">
-        <v>2.708547115325928</v>
+        <v>2.501128673553467</v>
       </c>
       <c r="D14" t="n">
-        <v>2.340174436569214</v>
+        <v>2.106153964996338</v>
       </c>
       <c r="E14" t="n">
-        <v>2.172819375991821</v>
+        <v>2.331561326980591</v>
       </c>
       <c r="F14" t="n">
-        <v>2.521298170089722</v>
+        <v>2.556544780731201</v>
       </c>
       <c r="G14" t="n">
-        <v>2.432206869125366</v>
+        <v>2.595394134521484</v>
       </c>
       <c r="H14" t="n">
-        <v>2.160044193267822</v>
+        <v>2.497147798538208</v>
       </c>
       <c r="I14" t="n">
-        <v>2.364137411117554</v>
+        <v>2.193446159362793</v>
       </c>
       <c r="J14" t="n">
-        <v>2.164822101593018</v>
+        <v>2.240284442901611</v>
       </c>
       <c r="K14" t="n">
-        <v>2.419828653335571</v>
+        <v>2.455745220184326</v>
       </c>
       <c r="L14" t="n">
-        <v>2.358069682121277</v>
+        <v>2.385235977172852</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.129291534423828</v>
+        <v>2.072224855422974</v>
       </c>
       <c r="C15" t="n">
-        <v>2.136654138565063</v>
+        <v>2.338565349578857</v>
       </c>
       <c r="D15" t="n">
-        <v>2.394240856170654</v>
+        <v>2.142551898956299</v>
       </c>
       <c r="E15" t="n">
-        <v>2.318422555923462</v>
+        <v>2.205403089523315</v>
       </c>
       <c r="F15" t="n">
-        <v>2.124093055725098</v>
+        <v>2.095158100128174</v>
       </c>
       <c r="G15" t="n">
-        <v>2.116775751113892</v>
+        <v>2.137057542800903</v>
       </c>
       <c r="H15" t="n">
-        <v>2.063676595687866</v>
+        <v>2.234330892562866</v>
       </c>
       <c r="I15" t="n">
-        <v>1.942867994308472</v>
+        <v>1.982955455780029</v>
       </c>
       <c r="J15" t="n">
-        <v>2.088302135467529</v>
+        <v>2.210390090942383</v>
       </c>
       <c r="K15" t="n">
-        <v>2.196383237838745</v>
+        <v>2.017858266830444</v>
       </c>
       <c r="L15" t="n">
-        <v>2.151070785522461</v>
+        <v>2.143649554252625</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.107687950134277</v>
+        <v>2.205410003662109</v>
       </c>
       <c r="C16" t="n">
-        <v>2.32529091835022</v>
+        <v>2.212884426116943</v>
       </c>
       <c r="D16" t="n">
-        <v>2.133718967437744</v>
+        <v>2.493640184402466</v>
       </c>
       <c r="E16" t="n">
-        <v>2.164938926696777</v>
+        <v>2.181450605392456</v>
       </c>
       <c r="F16" t="n">
-        <v>2.22506046295166</v>
+        <v>2.230314493179321</v>
       </c>
       <c r="G16" t="n">
-        <v>2.558796882629395</v>
+        <v>2.277708530426025</v>
       </c>
       <c r="H16" t="n">
-        <v>2.161989450454712</v>
+        <v>2.325639724731445</v>
       </c>
       <c r="I16" t="n">
-        <v>2.137226581573486</v>
+        <v>2.309623718261719</v>
       </c>
       <c r="J16" t="n">
-        <v>2.314630508422852</v>
+        <v>2.378948926925659</v>
       </c>
       <c r="K16" t="n">
-        <v>2.174893379211426</v>
+        <v>2.068228721618652</v>
       </c>
       <c r="L16" t="n">
-        <v>2.230423402786255</v>
+        <v>2.26838493347168</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.077313899993896</v>
+        <v>2.027843236923218</v>
       </c>
       <c r="C17" t="n">
-        <v>2.024054050445557</v>
+        <v>2.142547130584717</v>
       </c>
       <c r="D17" t="n">
-        <v>2.212053775787354</v>
+        <v>2.123095035552979</v>
       </c>
       <c r="E17" t="n">
-        <v>2.198116540908813</v>
+        <v>2.121094465255737</v>
       </c>
       <c r="F17" t="n">
-        <v>1.989967107772827</v>
+        <v>2.145043849945068</v>
       </c>
       <c r="G17" t="n">
-        <v>2.034219026565552</v>
+        <v>2.156522989273071</v>
       </c>
       <c r="H17" t="n">
-        <v>2.223303556442261</v>
+        <v>2.250266313552856</v>
       </c>
       <c r="I17" t="n">
-        <v>2.284520149230957</v>
+        <v>2.146560192108154</v>
       </c>
       <c r="J17" t="n">
-        <v>2.098505735397339</v>
+        <v>2.098161935806274</v>
       </c>
       <c r="K17" t="n">
-        <v>1.940006732940674</v>
+        <v>2.440787315368652</v>
       </c>
       <c r="L17" t="n">
-        <v>2.108206057548523</v>
+        <v>2.165192246437073</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.447140693664551</v>
+        <v>2.315614461898804</v>
       </c>
       <c r="C18" t="n">
-        <v>2.255982398986816</v>
+        <v>2.368957996368408</v>
       </c>
       <c r="D18" t="n">
-        <v>2.445510625839233</v>
+        <v>2.578442573547363</v>
       </c>
       <c r="E18" t="n">
-        <v>2.22103476524353</v>
+        <v>2.27522611618042</v>
       </c>
       <c r="F18" t="n">
-        <v>2.429621696472168</v>
+        <v>2.372971534729004</v>
       </c>
       <c r="G18" t="n">
-        <v>2.296006441116333</v>
+        <v>2.351053476333618</v>
       </c>
       <c r="H18" t="n">
-        <v>2.342350721359253</v>
+        <v>2.221327781677246</v>
       </c>
       <c r="I18" t="n">
-        <v>2.270107746124268</v>
+        <v>2.3006432056427</v>
       </c>
       <c r="J18" t="n">
-        <v>2.247695446014404</v>
+        <v>2.342536211013794</v>
       </c>
       <c r="K18" t="n">
-        <v>2.49787974357605</v>
+        <v>2.273716449737549</v>
       </c>
       <c r="L18" t="n">
-        <v>2.34533302783966</v>
+        <v>2.340048980712891</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.241619348526001</v>
+        <v>2.341554641723633</v>
       </c>
       <c r="C19" t="n">
-        <v>2.115235567092896</v>
+        <v>2.013871431350708</v>
       </c>
       <c r="D19" t="n">
-        <v>2.208670377731323</v>
+        <v>2.368975877761841</v>
       </c>
       <c r="E19" t="n">
-        <v>2.200814962387085</v>
+        <v>2.21736741065979</v>
       </c>
       <c r="F19" t="n">
-        <v>2.189357280731201</v>
+        <v>2.392901659011841</v>
       </c>
       <c r="G19" t="n">
-        <v>2.011263847351074</v>
+        <v>2.196425676345825</v>
       </c>
       <c r="H19" t="n">
-        <v>2.300731182098389</v>
+        <v>2.186424255371094</v>
       </c>
       <c r="I19" t="n">
-        <v>2.207804203033447</v>
+        <v>2.236308574676514</v>
       </c>
       <c r="J19" t="n">
-        <v>2.132145166397095</v>
+        <v>2.098157644271851</v>
       </c>
       <c r="K19" t="n">
-        <v>2.109400272369385</v>
+        <v>2.278704643249512</v>
       </c>
       <c r="L19" t="n">
-        <v>2.171704220771789</v>
+        <v>2.233069181442261</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.338994264602661</v>
+        <v>2.427820682525635</v>
       </c>
       <c r="C20" t="n">
-        <v>2.178755044937134</v>
+        <v>2.093189716339111</v>
       </c>
       <c r="D20" t="n">
-        <v>2.171271324157715</v>
+        <v>2.29866099357605</v>
       </c>
       <c r="E20" t="n">
-        <v>2.506963014602661</v>
+        <v>2.005888223648071</v>
       </c>
       <c r="F20" t="n">
-        <v>2.199081182479858</v>
+        <v>2.358494520187378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.144555330276489</v>
+        <v>2.183466672897339</v>
       </c>
       <c r="H20" t="n">
-        <v>2.264391899108887</v>
+        <v>2.35203218460083</v>
       </c>
       <c r="I20" t="n">
-        <v>2.179914474487305</v>
+        <v>2.331574678421021</v>
       </c>
       <c r="J20" t="n">
-        <v>2.162648677825928</v>
+        <v>2.492164134979248</v>
       </c>
       <c r="K20" t="n">
-        <v>2.164096593856812</v>
+        <v>2.826817989349365</v>
       </c>
       <c r="L20" t="n">
-        <v>2.231067180633545</v>
+        <v>2.337010979652405</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.265651226043701</v>
+        <v>2.30664324760437</v>
       </c>
       <c r="C21" t="n">
-        <v>2.288271903991699</v>
+        <v>2.4298255443573</v>
       </c>
       <c r="D21" t="n">
-        <v>2.241506099700928</v>
+        <v>2.318606615066528</v>
       </c>
       <c r="E21" t="n">
-        <v>2.325637817382812</v>
+        <v>2.290672540664673</v>
       </c>
       <c r="F21" t="n">
-        <v>2.20878005027771</v>
+        <v>2.010870933532715</v>
       </c>
       <c r="G21" t="n">
-        <v>2.247222661972046</v>
+        <v>2.37796688079834</v>
       </c>
       <c r="H21" t="n">
-        <v>2.16036057472229</v>
+        <v>2.115108013153076</v>
       </c>
       <c r="I21" t="n">
-        <v>2.345604419708252</v>
+        <v>2.380939722061157</v>
       </c>
       <c r="J21" t="n">
-        <v>2.291529893875122</v>
+        <v>2.141040325164795</v>
       </c>
       <c r="K21" t="n">
-        <v>2.271764278411865</v>
+        <v>2.378955125808716</v>
       </c>
       <c r="L21" t="n">
-        <v>2.264632892608643</v>
+        <v>2.275062894821167</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.114702701568604</v>
+        <v>2.216356039047241</v>
       </c>
       <c r="C22" t="n">
-        <v>2.227143526077271</v>
+        <v>2.194408655166626</v>
       </c>
       <c r="D22" t="n">
-        <v>2.216498136520386</v>
+        <v>2.307630062103271</v>
       </c>
       <c r="E22" t="n">
-        <v>2.134662866592407</v>
+        <v>2.247810840606689</v>
       </c>
       <c r="F22" t="n">
-        <v>2.126983404159546</v>
+        <v>2.154045104980469</v>
       </c>
       <c r="G22" t="n">
-        <v>2.105520009994507</v>
+        <v>2.124083995819092</v>
       </c>
       <c r="H22" t="n">
-        <v>2.071359157562256</v>
+        <v>2.197412729263306</v>
       </c>
       <c r="I22" t="n">
-        <v>2.137325048446655</v>
+        <v>2.135571718215942</v>
       </c>
       <c r="J22" t="n">
-        <v>2.100246429443359</v>
+        <v>2.080703020095825</v>
       </c>
       <c r="K22" t="n">
-        <v>2.205188274383545</v>
+        <v>2.166496515274048</v>
       </c>
       <c r="L22" t="n">
-        <v>2.143962955474854</v>
+        <v>2.182451868057251</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>2.155894994735718</v>
+        <v>1.971989631652832</v>
       </c>
       <c r="C23" t="n">
-        <v>2.031936407089233</v>
+        <v>2.213398694992065</v>
       </c>
       <c r="D23" t="n">
-        <v>1.978938579559326</v>
+        <v>1.878714561462402</v>
       </c>
       <c r="E23" t="n">
-        <v>1.953428745269775</v>
+        <v>1.993413686752319</v>
       </c>
       <c r="F23" t="n">
-        <v>1.953083276748657</v>
+        <v>1.903661727905273</v>
       </c>
       <c r="G23" t="n">
-        <v>1.947098255157471</v>
+        <v>2.140560626983643</v>
       </c>
       <c r="H23" t="n">
-        <v>1.884860515594482</v>
+        <v>2.018879175186157</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9338538646698</v>
+        <v>1.972977161407471</v>
       </c>
       <c r="J23" t="n">
-        <v>2.065775871276855</v>
+        <v>1.921603441238403</v>
       </c>
       <c r="K23" t="n">
-        <v>1.882113933563232</v>
+        <v>2.088594198226929</v>
       </c>
       <c r="L23" t="n">
-        <v>1.978698444366455</v>
+        <v>2.01037929058075</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1.919005632400513</v>
+        <v>2.060637235641479</v>
       </c>
       <c r="C24" t="n">
-        <v>1.967234373092651</v>
+        <v>2.165396928787231</v>
       </c>
       <c r="D24" t="n">
-        <v>2.036096811294556</v>
+        <v>2.003786563873291</v>
       </c>
       <c r="E24" t="n">
-        <v>1.89317798614502</v>
+        <v>1.907537937164307</v>
       </c>
       <c r="F24" t="n">
-        <v>2.094335794448853</v>
+        <v>2.073112487792969</v>
       </c>
       <c r="G24" t="n">
-        <v>1.906127452850342</v>
+        <v>2.011766195297241</v>
       </c>
       <c r="H24" t="n">
-        <v>1.904739856719971</v>
+        <v>2.203280925750732</v>
       </c>
       <c r="I24" t="n">
-        <v>1.958290100097656</v>
+        <v>2.112998962402344</v>
       </c>
       <c r="J24" t="n">
-        <v>2.030233144760132</v>
+        <v>2.029754638671875</v>
       </c>
       <c r="K24" t="n">
-        <v>1.949900388717651</v>
+        <v>2.141037464141846</v>
       </c>
       <c r="L24" t="n">
-        <v>1.965914154052734</v>
+        <v>2.070930933952332</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.321820974349976</v>
+        <v>2.329442739486694</v>
       </c>
       <c r="C25" t="n">
-        <v>2.196323871612549</v>
+        <v>2.275577306747437</v>
       </c>
       <c r="D25" t="n">
-        <v>2.232235670089722</v>
+        <v>1.936453819274902</v>
       </c>
       <c r="E25" t="n">
-        <v>2.233723640441895</v>
+        <v>2.123968839645386</v>
       </c>
       <c r="F25" t="n">
-        <v>2.206184864044189</v>
+        <v>1.922508716583252</v>
       </c>
       <c r="G25" t="n">
-        <v>2.139807462692261</v>
+        <v>2.283575534820557</v>
       </c>
       <c r="H25" t="n">
-        <v>2.291001081466675</v>
+        <v>2.287547588348389</v>
       </c>
       <c r="I25" t="n">
-        <v>2.173338890075684</v>
+        <v>2.038696527481079</v>
       </c>
       <c r="J25" t="n">
-        <v>2.080561637878418</v>
+        <v>2.187347650527954</v>
       </c>
       <c r="K25" t="n">
-        <v>2.283526182174683</v>
+        <v>2.351926565170288</v>
       </c>
       <c r="L25" t="n">
-        <v>2.215852427482605</v>
+        <v>2.173704528808594</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.38986349105835</v>
+        <v>2.393784999847412</v>
       </c>
       <c r="C26" t="n">
-        <v>2.311036348342896</v>
+        <v>2.177823066711426</v>
       </c>
       <c r="D26" t="n">
-        <v>2.195878505706787</v>
+        <v>2.427188873291016</v>
       </c>
       <c r="E26" t="n">
-        <v>2.304126024246216</v>
+        <v>2.29203987121582</v>
       </c>
       <c r="F26" t="n">
-        <v>2.428462982177734</v>
+        <v>2.336935043334961</v>
       </c>
       <c r="G26" t="n">
-        <v>2.451723098754883</v>
+        <v>2.400760650634766</v>
       </c>
       <c r="H26" t="n">
-        <v>2.309730768203735</v>
+        <v>2.353366851806641</v>
       </c>
       <c r="I26" t="n">
-        <v>2.370374917984009</v>
+        <v>2.471068143844604</v>
       </c>
       <c r="J26" t="n">
-        <v>2.44930362701416</v>
+        <v>2.421715259552002</v>
       </c>
       <c r="K26" t="n">
-        <v>2.307790517807007</v>
+        <v>2.287559270858765</v>
       </c>
       <c r="L26" t="n">
-        <v>2.351829028129578</v>
+        <v>2.356224203109741</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1.950636863708496</v>
+        <v>2.114994287490845</v>
       </c>
       <c r="C27" t="n">
-        <v>2.048053979873657</v>
+        <v>1.976861715316772</v>
       </c>
       <c r="D27" t="n">
-        <v>2.297824859619141</v>
+        <v>2.236191749572754</v>
       </c>
       <c r="E27" t="n">
-        <v>1.951358795166016</v>
+        <v>2.097063779830933</v>
       </c>
       <c r="F27" t="n">
-        <v>2.095714807510376</v>
+        <v>2.089081287384033</v>
       </c>
       <c r="G27" t="n">
-        <v>2.009640455245972</v>
+        <v>2.208255529403687</v>
       </c>
       <c r="H27" t="n">
-        <v>2.210864543914795</v>
+        <v>2.002785205841064</v>
       </c>
       <c r="I27" t="n">
-        <v>2.11367130279541</v>
+        <v>2.177335977554321</v>
       </c>
       <c r="J27" t="n">
-        <v>2.032106161117554</v>
+        <v>2.19330096244812</v>
       </c>
       <c r="K27" t="n">
-        <v>2.133439302444458</v>
+        <v>2.292047500610352</v>
       </c>
       <c r="L27" t="n">
-        <v>2.084331107139588</v>
+        <v>2.138791799545288</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.134323596954346</v>
+        <v>1.937458753585815</v>
       </c>
       <c r="C28" t="n">
-        <v>2.050173282623291</v>
+        <v>2.104022026062012</v>
       </c>
       <c r="D28" t="n">
-        <v>2.046347618103027</v>
+        <v>2.239171743392944</v>
       </c>
       <c r="E28" t="n">
-        <v>1.981670618057251</v>
+        <v>2.143454074859619</v>
       </c>
       <c r="F28" t="n">
-        <v>1.991923570632935</v>
+        <v>2.114991664886475</v>
       </c>
       <c r="G28" t="n">
-        <v>2.096890926361084</v>
+        <v>2.067623853683472</v>
       </c>
       <c r="H28" t="n">
-        <v>2.274205684661865</v>
+        <v>2.333953619003296</v>
       </c>
       <c r="I28" t="n">
-        <v>2.192763090133667</v>
+        <v>2.088563680648804</v>
       </c>
       <c r="J28" t="n">
-        <v>2.165671586990356</v>
+        <v>2.086086273193359</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9953293800354</v>
+        <v>2.102049589157104</v>
       </c>
       <c r="L28" t="n">
-        <v>2.092929935455322</v>
+        <v>2.12173752784729</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.085757732391357</v>
+        <v>2.222216606140137</v>
       </c>
       <c r="C29" t="n">
-        <v>2.294320344924927</v>
+        <v>2.179826498031616</v>
       </c>
       <c r="D29" t="n">
-        <v>2.059075832366943</v>
+        <v>2.062326908111572</v>
       </c>
       <c r="E29" t="n">
-        <v>2.045314311981201</v>
+        <v>2.267785549163818</v>
       </c>
       <c r="F29" t="n">
-        <v>2.133668184280396</v>
+        <v>1.937554121017456</v>
       </c>
       <c r="G29" t="n">
-        <v>2.051726102828979</v>
+        <v>2.126083135604858</v>
       </c>
       <c r="H29" t="n">
-        <v>2.130208015441895</v>
+        <v>2.12111234664917</v>
       </c>
       <c r="I29" t="n">
-        <v>2.091756343841553</v>
+        <v>2.19640064239502</v>
       </c>
       <c r="J29" t="n">
-        <v>2.145300626754761</v>
+        <v>2.06425404548645</v>
       </c>
       <c r="K29" t="n">
-        <v>2.074021100997925</v>
+        <v>2.153006076812744</v>
       </c>
       <c r="L29" t="n">
-        <v>2.111114859580994</v>
+        <v>2.133056592941284</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.149755716323853</v>
+        <v>2.258247375488281</v>
       </c>
       <c r="C30" t="n">
-        <v>2.195824146270752</v>
+        <v>2.269726037979126</v>
       </c>
       <c r="D30" t="n">
-        <v>2.098745584487915</v>
+        <v>2.357511758804321</v>
       </c>
       <c r="E30" t="n">
-        <v>2.112931489944458</v>
+        <v>2.313605546951294</v>
       </c>
       <c r="F30" t="n">
-        <v>2.234400510787964</v>
+        <v>2.152538776397705</v>
       </c>
       <c r="G30" t="n">
-        <v>2.301943778991699</v>
+        <v>2.157998561859131</v>
       </c>
       <c r="H30" t="n">
-        <v>2.287332534790039</v>
+        <v>2.163484573364258</v>
       </c>
       <c r="I30" t="n">
-        <v>2.235028982162476</v>
+        <v>2.282716751098633</v>
       </c>
       <c r="J30" t="n">
-        <v>2.185342073440552</v>
+        <v>2.044773578643799</v>
       </c>
       <c r="K30" t="n">
-        <v>2.056848764419556</v>
+        <v>2.206404209136963</v>
       </c>
       <c r="L30" t="n">
-        <v>2.185815358161926</v>
+        <v>2.220700716972351</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.852800846099854</v>
+        <v>1.907639026641846</v>
       </c>
       <c r="C31" t="n">
-        <v>1.852221965789795</v>
+        <v>1.8508620262146</v>
       </c>
       <c r="D31" t="n">
-        <v>1.812756538391113</v>
+        <v>1.828347444534302</v>
       </c>
       <c r="E31" t="n">
-        <v>1.809564352035522</v>
+        <v>1.952525615692139</v>
       </c>
       <c r="F31" t="n">
-        <v>1.864607810974121</v>
+        <v>2.050288915634155</v>
       </c>
       <c r="G31" t="n">
-        <v>2.017434597015381</v>
+        <v>1.974970102310181</v>
       </c>
       <c r="H31" t="n">
-        <v>2.007030963897705</v>
+        <v>1.803455352783203</v>
       </c>
       <c r="I31" t="n">
-        <v>1.91984486579895</v>
+        <v>1.886196136474609</v>
       </c>
       <c r="J31" t="n">
-        <v>1.836316347122192</v>
+        <v>1.844805240631104</v>
       </c>
       <c r="K31" t="n">
-        <v>1.841034173965454</v>
+        <v>1.929578304290771</v>
       </c>
       <c r="L31" t="n">
-        <v>1.881361246109009</v>
+        <v>1.902866816520691</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>2.068676233291626</v>
+        <v>2.060743570327759</v>
       </c>
       <c r="C32" t="n">
-        <v>2.045520782470703</v>
+        <v>1.97695517539978</v>
       </c>
       <c r="D32" t="n">
-        <v>2.228826999664307</v>
+        <v>2.106140851974487</v>
       </c>
       <c r="E32" t="n">
-        <v>1.937721252441406</v>
+        <v>1.962015867233276</v>
       </c>
       <c r="F32" t="n">
-        <v>1.903743982315063</v>
+        <v>1.886692047119141</v>
       </c>
       <c r="G32" t="n">
-        <v>1.952646970748901</v>
+        <v>1.997416019439697</v>
       </c>
       <c r="H32" t="n">
-        <v>1.93692946434021</v>
+        <v>2.042792081832886</v>
       </c>
       <c r="I32" t="n">
-        <v>1.951387405395508</v>
+        <v>1.913626194000244</v>
       </c>
       <c r="J32" t="n">
-        <v>1.942036628723145</v>
+        <v>2.397899866104126</v>
       </c>
       <c r="K32" t="n">
-        <v>1.914817571640015</v>
+        <v>1.967986106872559</v>
       </c>
       <c r="L32" t="n">
-        <v>1.988230729103088</v>
+        <v>2.031226778030395</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.122656106948853</v>
+        <v>2.123100519180298</v>
       </c>
       <c r="C33" t="n">
-        <v>2.017584323883057</v>
+        <v>2.105135202407837</v>
       </c>
       <c r="D33" t="n">
-        <v>2.134464502334595</v>
+        <v>2.043812274932861</v>
       </c>
       <c r="E33" t="n">
-        <v>1.983490467071533</v>
+        <v>2.133078336715698</v>
       </c>
       <c r="F33" t="n">
-        <v>1.931152105331421</v>
+        <v>2.147028923034668</v>
       </c>
       <c r="G33" t="n">
-        <v>2.274795055389404</v>
+        <v>2.128073930740356</v>
       </c>
       <c r="H33" t="n">
-        <v>2.07836651802063</v>
+        <v>2.10315203666687</v>
       </c>
       <c r="I33" t="n">
-        <v>2.009516716003418</v>
+        <v>2.052286386489868</v>
       </c>
       <c r="J33" t="n">
-        <v>1.976021528244019</v>
+        <v>2.094061136245728</v>
       </c>
       <c r="K33" t="n">
-        <v>1.999484539031982</v>
+        <v>2.309831380844116</v>
       </c>
       <c r="L33" t="n">
-        <v>2.052753186225891</v>
+        <v>2.12395601272583</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1.862815380096436</v>
+        <v>1.85427451133728</v>
       </c>
       <c r="C34" t="n">
-        <v>1.811066389083862</v>
+        <v>1.883710861206055</v>
       </c>
       <c r="D34" t="n">
-        <v>1.878596544265747</v>
+        <v>2.038800477981567</v>
       </c>
       <c r="E34" t="n">
-        <v>1.877163887023926</v>
+        <v>2.171485662460327</v>
       </c>
       <c r="F34" t="n">
-        <v>1.94016432762146</v>
+        <v>1.948565006256104</v>
       </c>
       <c r="G34" t="n">
-        <v>2.048839569091797</v>
+        <v>1.88270378112793</v>
       </c>
       <c r="H34" t="n">
-        <v>2.025699615478516</v>
+        <v>1.752559185028076</v>
       </c>
       <c r="I34" t="n">
-        <v>1.999235868453979</v>
+        <v>1.989135503768921</v>
       </c>
       <c r="J34" t="n">
-        <v>1.898751974105835</v>
+        <v>1.875118017196655</v>
       </c>
       <c r="K34" t="n">
-        <v>1.884852170944214</v>
+        <v>1.940951824188232</v>
       </c>
       <c r="L34" t="n">
-        <v>1.922718572616577</v>
+        <v>1.933730483055115</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.325177431106567</v>
+        <v>2.36466908454895</v>
       </c>
       <c r="C35" t="n">
-        <v>2.189551591873169</v>
+        <v>2.257750749588013</v>
       </c>
       <c r="D35" t="n">
-        <v>2.262913465499878</v>
+        <v>2.346536636352539</v>
       </c>
       <c r="E35" t="n">
-        <v>2.260327816009521</v>
+        <v>2.428329467773438</v>
       </c>
       <c r="F35" t="n">
-        <v>2.315512180328369</v>
+        <v>2.34052586555481</v>
       </c>
       <c r="G35" t="n">
-        <v>2.544758558273315</v>
+        <v>2.268722772598267</v>
       </c>
       <c r="H35" t="n">
-        <v>2.54141092300415</v>
+        <v>2.228309631347656</v>
       </c>
       <c r="I35" t="n">
-        <v>2.269749641418457</v>
+        <v>2.366495847702026</v>
       </c>
       <c r="J35" t="n">
-        <v>2.37511134147644</v>
+        <v>2.196413516998291</v>
       </c>
       <c r="K35" t="n">
-        <v>2.250014781951904</v>
+        <v>2.508130550384521</v>
       </c>
       <c r="L35" t="n">
-        <v>2.333452773094177</v>
+        <v>2.330588412284851</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1.945332050323486</v>
+        <v>1.869736433029175</v>
       </c>
       <c r="C36" t="n">
-        <v>2.092214345932007</v>
+        <v>1.944544553756714</v>
       </c>
       <c r="D36" t="n">
-        <v>1.851113319396973</v>
+        <v>1.895675659179688</v>
       </c>
       <c r="E36" t="n">
-        <v>1.93216347694397</v>
+        <v>2.039321899414062</v>
       </c>
       <c r="F36" t="n">
-        <v>1.853187799453735</v>
+        <v>1.933569431304932</v>
       </c>
       <c r="G36" t="n">
-        <v>1.848152637481689</v>
+        <v>1.892684459686279</v>
       </c>
       <c r="H36" t="n">
-        <v>2.002153635025024</v>
+        <v>1.952522754669189</v>
       </c>
       <c r="I36" t="n">
-        <v>1.861187219619751</v>
+        <v>2.058268070220947</v>
       </c>
       <c r="J36" t="n">
-        <v>1.850544691085815</v>
+        <v>1.994915962219238</v>
       </c>
       <c r="K36" t="n">
-        <v>1.840090751647949</v>
+        <v>1.883699655532837</v>
       </c>
       <c r="L36" t="n">
-        <v>1.90761399269104</v>
+        <v>1.946493887901306</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.206846237182617</v>
+        <v>2.246273994445801</v>
       </c>
       <c r="C37" t="n">
-        <v>2.20389199256897</v>
+        <v>2.096158981323242</v>
       </c>
       <c r="D37" t="n">
-        <v>2.379176616668701</v>
+        <v>2.529086112976074</v>
       </c>
       <c r="E37" t="n">
-        <v>2.285905838012695</v>
+        <v>2.155521631240845</v>
       </c>
       <c r="F37" t="n">
-        <v>2.362612962722778</v>
+        <v>2.330562829971313</v>
       </c>
       <c r="G37" t="n">
-        <v>2.182089567184448</v>
+        <v>2.357018709182739</v>
       </c>
       <c r="H37" t="n">
-        <v>2.310354232788086</v>
+        <v>2.340543508529663</v>
       </c>
       <c r="I37" t="n">
-        <v>2.122403621673584</v>
+        <v>2.275726318359375</v>
       </c>
       <c r="J37" t="n">
-        <v>2.23781681060791</v>
+        <v>2.307624101638794</v>
       </c>
       <c r="K37" t="n">
-        <v>2.160520792007446</v>
+        <v>2.226337671279907</v>
       </c>
       <c r="L37" t="n">
-        <v>2.245161867141724</v>
+        <v>2.286485385894776</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.472980976104736</v>
+        <v>2.595403671264648</v>
       </c>
       <c r="C38" t="n">
-        <v>2.557123184204102</v>
+        <v>2.526071786880493</v>
       </c>
       <c r="D38" t="n">
-        <v>2.585821628570557</v>
+        <v>2.653734445571899</v>
       </c>
       <c r="E38" t="n">
-        <v>2.510479211807251</v>
+        <v>2.863696813583374</v>
       </c>
       <c r="F38" t="n">
-        <v>2.61224889755249</v>
+        <v>2.527058839797974</v>
       </c>
       <c r="G38" t="n">
-        <v>2.41256046295166</v>
+        <v>2.707644939422607</v>
       </c>
       <c r="H38" t="n">
-        <v>2.524693727493286</v>
+        <v>2.755993366241455</v>
       </c>
       <c r="I38" t="n">
-        <v>2.570968151092529</v>
+        <v>2.759465932846069</v>
       </c>
       <c r="J38" t="n">
-        <v>2.776217699050903</v>
+        <v>2.462234258651733</v>
       </c>
       <c r="K38" t="n">
-        <v>2.503952741622925</v>
+        <v>2.473211526870728</v>
       </c>
       <c r="L38" t="n">
-        <v>2.552704668045044</v>
+        <v>2.632451558113098</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.159672260284424</v>
+        <v>2.251260280609131</v>
       </c>
       <c r="C39" t="n">
-        <v>2.128580808639526</v>
+        <v>2.269751310348511</v>
       </c>
       <c r="D39" t="n">
-        <v>2.247498035430908</v>
+        <v>2.278702974319458</v>
       </c>
       <c r="E39" t="n">
-        <v>2.150602340698242</v>
+        <v>2.221402406692505</v>
       </c>
       <c r="F39" t="n">
-        <v>2.256948232650757</v>
+        <v>2.403865098953247</v>
       </c>
       <c r="G39" t="n">
-        <v>2.240822553634644</v>
+        <v>2.504136800765991</v>
       </c>
       <c r="H39" t="n">
-        <v>2.2411789894104</v>
+        <v>2.243274211883545</v>
       </c>
       <c r="I39" t="n">
-        <v>2.367488622665405</v>
+        <v>2.501177072525024</v>
       </c>
       <c r="J39" t="n">
-        <v>2.178977966308594</v>
+        <v>2.153538465499878</v>
       </c>
       <c r="K39" t="n">
-        <v>2.53000807762146</v>
+        <v>2.330562114715576</v>
       </c>
       <c r="L39" t="n">
-        <v>2.250177788734436</v>
+        <v>2.315767073631287</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.10194730758667</v>
+        <v>2.137056112289429</v>
       </c>
       <c r="C40" t="n">
-        <v>2.071304798126221</v>
+        <v>2.160495281219482</v>
       </c>
       <c r="D40" t="n">
-        <v>2.161607980728149</v>
+        <v>2.134071350097656</v>
       </c>
       <c r="E40" t="n">
-        <v>2.054361343383789</v>
+        <v>2.105130910873413</v>
       </c>
       <c r="F40" t="n">
-        <v>2.094481706619263</v>
+        <v>2.183440685272217</v>
       </c>
       <c r="G40" t="n">
-        <v>2.117873191833496</v>
+        <v>2.065725326538086</v>
       </c>
       <c r="H40" t="n">
-        <v>2.047609329223633</v>
+        <v>2.084222316741943</v>
       </c>
       <c r="I40" t="n">
-        <v>2.12884259223938</v>
+        <v>2.083208560943604</v>
       </c>
       <c r="J40" t="n">
-        <v>2.083362340927124</v>
+        <v>1.994921445846558</v>
       </c>
       <c r="K40" t="n">
-        <v>2.122716665267944</v>
+        <v>2.057266235351562</v>
       </c>
       <c r="L40" t="n">
-        <v>2.098410725593567</v>
+        <v>2.100553822517395</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.455496072769165</v>
+        <v>2.189420461654663</v>
       </c>
       <c r="C41" t="n">
-        <v>2.499671459197998</v>
+        <v>2.385426759719849</v>
       </c>
       <c r="D41" t="n">
-        <v>2.374307632446289</v>
+        <v>2.285703897476196</v>
       </c>
       <c r="E41" t="n">
-        <v>2.412522792816162</v>
+        <v>2.313600301742554</v>
       </c>
       <c r="F41" t="n">
-        <v>2.371212959289551</v>
+        <v>2.336051225662231</v>
       </c>
       <c r="G41" t="n">
-        <v>2.370973110198975</v>
+        <v>2.332553863525391</v>
       </c>
       <c r="H41" t="n">
-        <v>2.348926782608032</v>
+        <v>2.341546297073364</v>
       </c>
       <c r="I41" t="n">
-        <v>2.150734663009644</v>
+        <v>2.196416854858398</v>
       </c>
       <c r="J41" t="n">
-        <v>2.449037313461304</v>
+        <v>2.324584484100342</v>
       </c>
       <c r="K41" t="n">
-        <v>2.412134408950806</v>
+        <v>2.210370063781738</v>
       </c>
       <c r="L41" t="n">
-        <v>2.384501719474792</v>
+        <v>2.291567420959473</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1.991478443145752</v>
+        <v>1.951532363891602</v>
       </c>
       <c r="C42" t="n">
-        <v>1.980459213256836</v>
+        <v>2.123607873916626</v>
       </c>
       <c r="D42" t="n">
-        <v>1.927897930145264</v>
+        <v>1.891164779663086</v>
       </c>
       <c r="E42" t="n">
-        <v>2.016181468963623</v>
+        <v>2.081218242645264</v>
       </c>
       <c r="F42" t="n">
-        <v>1.987638711929321</v>
+        <v>2.14255428314209</v>
       </c>
       <c r="G42" t="n">
-        <v>2.098737716674805</v>
+        <v>2.017862796783447</v>
       </c>
       <c r="H42" t="n">
-        <v>2.163670063018799</v>
+        <v>2.043792009353638</v>
       </c>
       <c r="I42" t="n">
-        <v>2.028321266174316</v>
+        <v>1.982951641082764</v>
       </c>
       <c r="J42" t="n">
-        <v>1.949297189712524</v>
+        <v>1.994936466217041</v>
       </c>
       <c r="K42" t="n">
-        <v>1.980177640914917</v>
+        <v>2.059748888015747</v>
       </c>
       <c r="L42" t="n">
-        <v>2.012385964393616</v>
+        <v>2.028936934471131</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.17272686958313</v>
+        <v>2.105143308639526</v>
       </c>
       <c r="C43" t="n">
-        <v>2.117297887802124</v>
+        <v>2.313609600067139</v>
       </c>
       <c r="D43" t="n">
-        <v>2.063717603683472</v>
+        <v>2.118616104125977</v>
       </c>
       <c r="E43" t="n">
-        <v>2.092862129211426</v>
+        <v>2.067716121673584</v>
       </c>
       <c r="F43" t="n">
-        <v>2.111837387084961</v>
+        <v>2.069277763366699</v>
       </c>
       <c r="G43" t="n">
-        <v>2.14012336730957</v>
+        <v>2.017862796783447</v>
       </c>
       <c r="H43" t="n">
-        <v>2.112539529800415</v>
+        <v>2.135070085525513</v>
       </c>
       <c r="I43" t="n">
-        <v>2.114257574081421</v>
+        <v>1.970977306365967</v>
       </c>
       <c r="J43" t="n">
-        <v>2.151212930679321</v>
+        <v>2.219352722167969</v>
       </c>
       <c r="K43" t="n">
-        <v>2.145330667495728</v>
+        <v>2.048284530639648</v>
       </c>
       <c r="L43" t="n">
-        <v>2.122190594673157</v>
+        <v>2.106591033935547</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.146310567855835</v>
+        <v>2.118119478225708</v>
       </c>
       <c r="C44" t="n">
-        <v>2.064264535903931</v>
+        <v>2.180448770523071</v>
       </c>
       <c r="D44" t="n">
-        <v>2.15720796585083</v>
+        <v>2.0687096118927</v>
       </c>
       <c r="E44" t="n">
-        <v>2.051315784454346</v>
+        <v>2.177454471588135</v>
       </c>
       <c r="F44" t="n">
-        <v>2.073998212814331</v>
+        <v>1.991931438446045</v>
       </c>
       <c r="G44" t="n">
-        <v>2.038678884506226</v>
+        <v>2.076228141784668</v>
       </c>
       <c r="H44" t="n">
-        <v>2.045491933822632</v>
+        <v>2.071713924407959</v>
       </c>
       <c r="I44" t="n">
-        <v>2.107578277587891</v>
+        <v>2.17746639251709</v>
       </c>
       <c r="J44" t="n">
-        <v>2.010205984115601</v>
+        <v>2.030831098556519</v>
       </c>
       <c r="K44" t="n">
-        <v>2.1180419921875</v>
+        <v>2.179466962814331</v>
       </c>
       <c r="L44" t="n">
-        <v>2.081309413909912</v>
+        <v>2.107237029075622</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>2.019362926483154</v>
+        <v>2.054293394088745</v>
       </c>
       <c r="C45" t="n">
-        <v>1.893632650375366</v>
+        <v>1.909652471542358</v>
       </c>
       <c r="D45" t="n">
-        <v>1.90083909034729</v>
+        <v>2.150032520294189</v>
       </c>
       <c r="E45" t="n">
-        <v>1.955581188201904</v>
+        <v>2.030836582183838</v>
       </c>
       <c r="F45" t="n">
-        <v>1.944375514984131</v>
+        <v>1.908639907836914</v>
       </c>
       <c r="G45" t="n">
-        <v>2.1888747215271</v>
+        <v>1.924603462219238</v>
       </c>
       <c r="H45" t="n">
-        <v>1.919596672058105</v>
+        <v>2.048794746398926</v>
       </c>
       <c r="I45" t="n">
-        <v>1.90267014503479</v>
+        <v>1.929581642150879</v>
       </c>
       <c r="J45" t="n">
-        <v>1.887521982192993</v>
+        <v>1.980961561203003</v>
       </c>
       <c r="K45" t="n">
-        <v>1.885628938674927</v>
+        <v>2.132126808166504</v>
       </c>
       <c r="L45" t="n">
-        <v>1.949808382987976</v>
+        <v>2.006952309608459</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>2.004914522171021</v>
+        <v>1.880210161209106</v>
       </c>
       <c r="C46" t="n">
-        <v>1.932830095291138</v>
+        <v>1.825353384017944</v>
       </c>
       <c r="D46" t="n">
-        <v>1.85053014755249</v>
+        <v>1.829368114471436</v>
       </c>
       <c r="E46" t="n">
-        <v>1.819119215011597</v>
+        <v>1.743066549301147</v>
       </c>
       <c r="F46" t="n">
-        <v>1.764892101287842</v>
+        <v>2.244799137115479</v>
       </c>
       <c r="G46" t="n">
-        <v>1.813811779022217</v>
+        <v>1.887191772460938</v>
       </c>
       <c r="H46" t="n">
-        <v>1.845673322677612</v>
+        <v>1.988941431045532</v>
       </c>
       <c r="I46" t="n">
-        <v>1.806967973709106</v>
+        <v>1.776472330093384</v>
       </c>
       <c r="J46" t="n">
-        <v>2.003021955490112</v>
+        <v>1.97897481918335</v>
       </c>
       <c r="K46" t="n">
-        <v>1.871166706085205</v>
+        <v>1.956507444381714</v>
       </c>
       <c r="L46" t="n">
-        <v>1.871292781829834</v>
+        <v>1.911088514328003</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.56810188293457</v>
+        <v>2.764991283416748</v>
       </c>
       <c r="C47" t="n">
-        <v>2.593642473220825</v>
+        <v>2.721561670303345</v>
       </c>
       <c r="D47" t="n">
-        <v>2.694672584533691</v>
+        <v>2.387940168380737</v>
       </c>
       <c r="E47" t="n">
-        <v>2.698776960372925</v>
+        <v>2.45275616645813</v>
       </c>
       <c r="F47" t="n">
-        <v>2.580044507980347</v>
+        <v>2.85825777053833</v>
       </c>
       <c r="G47" t="n">
-        <v>2.658894538879395</v>
+        <v>2.561970472335815</v>
       </c>
       <c r="H47" t="n">
-        <v>2.480711460113525</v>
+        <v>2.699680328369141</v>
       </c>
       <c r="I47" t="n">
-        <v>3.011406898498535</v>
+        <v>2.503125905990601</v>
       </c>
       <c r="J47" t="n">
-        <v>2.49066948890686</v>
+        <v>2.656739234924316</v>
       </c>
       <c r="K47" t="n">
-        <v>2.674644231796265</v>
+        <v>2.947000741958618</v>
       </c>
       <c r="L47" t="n">
-        <v>2.645156502723694</v>
+        <v>2.655402374267578</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.14496898651123</v>
+        <v>2.346043348312378</v>
       </c>
       <c r="C48" t="n">
-        <v>2.168864250183105</v>
+        <v>2.116103172302246</v>
       </c>
       <c r="D48" t="n">
-        <v>2.405799627304077</v>
+        <v>2.147044897079468</v>
       </c>
       <c r="E48" t="n">
-        <v>2.226865768432617</v>
+        <v>2.182454109191895</v>
       </c>
       <c r="F48" t="n">
-        <v>2.208540201187134</v>
+        <v>2.187429189682007</v>
       </c>
       <c r="G48" t="n">
-        <v>2.180337190628052</v>
+        <v>2.182445049285889</v>
       </c>
       <c r="H48" t="n">
-        <v>2.204140901565552</v>
+        <v>2.122089385986328</v>
       </c>
       <c r="I48" t="n">
-        <v>2.264995813369751</v>
+        <v>2.177465438842773</v>
       </c>
       <c r="J48" t="n">
-        <v>2.162772178649902</v>
+        <v>2.180941104888916</v>
       </c>
       <c r="K48" t="n">
-        <v>2.124196290969849</v>
+        <v>2.303122758865356</v>
       </c>
       <c r="L48" t="n">
-        <v>2.209148120880127</v>
+        <v>2.194513845443725</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.157165050506592</v>
+        <v>2.276187419891357</v>
       </c>
       <c r="C49" t="n">
-        <v>2.36750316619873</v>
+        <v>2.203385591506958</v>
       </c>
       <c r="D49" t="n">
-        <v>2.212975740432739</v>
+        <v>2.491180181503296</v>
       </c>
       <c r="E49" t="n">
-        <v>2.256000995635986</v>
+        <v>2.186430215835571</v>
       </c>
       <c r="F49" t="n">
-        <v>2.295694828033447</v>
+        <v>2.273705959320068</v>
       </c>
       <c r="G49" t="n">
-        <v>2.228755712509155</v>
+        <v>2.330559253692627</v>
       </c>
       <c r="H49" t="n">
-        <v>2.256751298904419</v>
+        <v>2.201419830322266</v>
       </c>
       <c r="I49" t="n">
-        <v>2.410125255584717</v>
+        <v>2.347543001174927</v>
       </c>
       <c r="J49" t="n">
-        <v>2.322511911392212</v>
+        <v>2.298655986785889</v>
       </c>
       <c r="K49" t="n">
-        <v>2.186676740646362</v>
+        <v>2.26373815536499</v>
       </c>
       <c r="L49" t="n">
-        <v>2.269416069984436</v>
+        <v>2.287280559539795</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.053407669067383</v>
+        <v>2.001898050308228</v>
       </c>
       <c r="C50" t="n">
-        <v>2.050266742706299</v>
+        <v>2.051782369613647</v>
       </c>
       <c r="D50" t="n">
-        <v>1.963768720626831</v>
+        <v>2.063250541687012</v>
       </c>
       <c r="E50" t="n">
-        <v>2.134491682052612</v>
+        <v>1.938565969467163</v>
       </c>
       <c r="F50" t="n">
-        <v>1.986991405487061</v>
+        <v>2.003900766372681</v>
       </c>
       <c r="G50" t="n">
-        <v>1.909096479415894</v>
+        <v>1.913635015487671</v>
       </c>
       <c r="H50" t="n">
-        <v>2.018543481826782</v>
+        <v>2.053288221359253</v>
       </c>
       <c r="I50" t="n">
-        <v>2.045532464981079</v>
+        <v>2.205394744873047</v>
       </c>
       <c r="J50" t="n">
-        <v>2.005615234375</v>
+        <v>2.113120317459106</v>
       </c>
       <c r="K50" t="n">
-        <v>1.941391706466675</v>
+        <v>1.982950210571289</v>
       </c>
       <c r="L50" t="n">
-        <v>2.010910558700561</v>
+        <v>2.03277862071991</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>2.158534288406372</v>
+        <v>1.926998615264893</v>
       </c>
       <c r="C51" t="n">
-        <v>1.998613834381104</v>
+        <v>1.848296880722046</v>
       </c>
       <c r="D51" t="n">
-        <v>1.941891670227051</v>
+        <v>2.048300504684448</v>
       </c>
       <c r="E51" t="n">
-        <v>1.990491151809692</v>
+        <v>1.864245653152466</v>
       </c>
       <c r="F51" t="n">
-        <v>1.92759108543396</v>
+        <v>2.051315069198608</v>
       </c>
       <c r="G51" t="n">
-        <v>1.893296480178833</v>
+        <v>1.924603700637817</v>
       </c>
       <c r="H51" t="n">
-        <v>1.893073797225952</v>
+        <v>1.94904613494873</v>
       </c>
       <c r="I51" t="n">
-        <v>1.987056016921997</v>
+        <v>1.96651816368103</v>
       </c>
       <c r="J51" t="n">
-        <v>1.854807138442993</v>
+        <v>2.075213193893433</v>
       </c>
       <c r="K51" t="n">
-        <v>1.883814334869385</v>
+        <v>1.970979452133179</v>
       </c>
       <c r="L51" t="n">
-        <v>1.952916979789734</v>
+        <v>1.962551736831665</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.166442537307739</v>
+        <v>2.246445765495301</v>
       </c>
       <c r="C52" t="n">
-        <v>2.175467123985291</v>
+        <v>2.298482847213745</v>
       </c>
       <c r="D52" t="n">
-        <v>2.203747148513794</v>
+        <v>2.277893052101135</v>
       </c>
       <c r="E52" t="n">
-        <v>2.163833465576172</v>
+        <v>2.23582528591156</v>
       </c>
       <c r="F52" t="n">
-        <v>2.151306009292603</v>
+        <v>2.240206289291382</v>
       </c>
       <c r="G52" t="n">
-        <v>2.17442437171936</v>
+        <v>2.231508054733276</v>
       </c>
       <c r="H52" t="n">
-        <v>2.167897634506226</v>
+        <v>2.278064780235291</v>
       </c>
       <c r="I52" t="n">
-        <v>2.176056551933288</v>
+        <v>2.273300061225891</v>
       </c>
       <c r="J52" t="n">
-        <v>2.157876205444336</v>
+        <v>2.252517352104187</v>
       </c>
       <c r="K52" t="n">
-        <v>2.150107913017273</v>
+        <v>2.261740856170654</v>
       </c>
       <c r="L52" t="n">
-        <v>2.168715896129608</v>
+        <v>2.259598434448242</v>
       </c>
     </row>
   </sheetData>
